--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293942</v>
+        <v>122291893</v>
       </c>
       <c r="B2" t="n">
-        <v>56824</v>
+        <v>56266</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337617</v>
+        <v>337535</v>
       </c>
       <c r="R2" t="n">
-        <v>6396884</v>
+        <v>6396829</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291893</v>
+        <v>122291921</v>
       </c>
       <c r="B3" t="n">
-        <v>56264</v>
+        <v>58206</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +798,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -838,10 +843,10 @@
         <v>337535</v>
       </c>
       <c r="R3" t="n">
-        <v>6396829</v>
+        <v>6396924</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293033</v>
+        <v>122293798</v>
       </c>
       <c r="B4" t="n">
-        <v>58077</v>
+        <v>57916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,25 +918,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337554</v>
+        <v>337473</v>
       </c>
       <c r="R4" t="n">
-        <v>6396883</v>
+        <v>6396849</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -980,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293798</v>
+        <v>122293033</v>
       </c>
       <c r="B5" t="n">
-        <v>57914</v>
+        <v>58079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1065,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337473</v>
+        <v>337554</v>
       </c>
       <c r="R5" t="n">
-        <v>6396849</v>
+        <v>6396883</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1095,12 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291936</v>
+        <v>122291895</v>
       </c>
       <c r="B6" t="n">
-        <v>58232</v>
+        <v>56266</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,40 +1148,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337654</v>
+        <v>337542</v>
       </c>
       <c r="R6" t="n">
-        <v>6396873</v>
+        <v>6396827</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,12 +1211,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291921</v>
+        <v>122293942</v>
       </c>
       <c r="B7" t="n">
-        <v>58204</v>
+        <v>56826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,16 +1263,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208245</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1289,14 +1285,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337535</v>
+        <v>337617</v>
       </c>
       <c r="R7" t="n">
-        <v>6396924</v>
+        <v>6396884</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,12 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1351,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1371,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291895</v>
+        <v>122291936</v>
       </c>
       <c r="B8" t="n">
-        <v>56264</v>
+        <v>58234</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,31 +1374,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337542</v>
+        <v>337654</v>
       </c>
       <c r="R8" t="n">
-        <v>6396827</v>
+        <v>6396873</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291893</v>
+        <v>122293033</v>
       </c>
       <c r="B2" t="n">
-        <v>56266</v>
+        <v>58079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337535</v>
+        <v>337554</v>
       </c>
       <c r="R2" t="n">
-        <v>6396829</v>
+        <v>6396883</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291921</v>
+        <v>122291893</v>
       </c>
       <c r="B3" t="n">
-        <v>58206</v>
+        <v>56266</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,40 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,10 +838,10 @@
         <v>337535</v>
       </c>
       <c r="R3" t="n">
-        <v>6396924</v>
+        <v>6396829</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -906,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293798</v>
+        <v>122291936</v>
       </c>
       <c r="B4" t="n">
-        <v>57916</v>
+        <v>58234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,9 +939,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337473</v>
+        <v>337654</v>
       </c>
       <c r="R4" t="n">
-        <v>6396849</v>
+        <v>6396873</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293033</v>
+        <v>122293942</v>
       </c>
       <c r="B5" t="n">
-        <v>58079</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337554</v>
+        <v>337617</v>
       </c>
       <c r="R5" t="n">
-        <v>6396883</v>
+        <v>6396884</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291895</v>
+        <v>122293798</v>
       </c>
       <c r="B6" t="n">
-        <v>56266</v>
+        <v>57916</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,31 +1148,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1181,13 +1185,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337542</v>
+        <v>337473</v>
       </c>
       <c r="R6" t="n">
-        <v>6396827</v>
+        <v>6396849</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,12 +1215,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,7 +1240,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1247,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293942</v>
+        <v>122291895</v>
       </c>
       <c r="B7" t="n">
-        <v>56826</v>
+        <v>56266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,35 +1263,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337617</v>
+        <v>337542</v>
       </c>
       <c r="R7" t="n">
-        <v>6396884</v>
+        <v>6396827</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291936</v>
+        <v>122291921</v>
       </c>
       <c r="B8" t="n">
-        <v>58234</v>
+        <v>58206</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337654</v>
+        <v>337535</v>
       </c>
       <c r="R8" t="n">
-        <v>6396873</v>
+        <v>6396924</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291921</v>
+        <v>122293798</v>
       </c>
       <c r="B2" t="n">
-        <v>58206</v>
+        <v>57916</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,14 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337535</v>
+        <v>337473</v>
       </c>
       <c r="R2" t="n">
-        <v>6396924</v>
+        <v>6396849</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291936</v>
+        <v>122293033</v>
       </c>
       <c r="B5" t="n">
-        <v>58234</v>
+        <v>58079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,20 +1028,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,14 +1054,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337654</v>
+        <v>337554</v>
       </c>
       <c r="R5" t="n">
-        <v>6396873</v>
+        <v>6396883</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,12 +1095,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1141,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293798</v>
+        <v>122291921</v>
       </c>
       <c r="B6" t="n">
-        <v>57916</v>
+        <v>58206</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,16 +1147,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>208245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,9 +1169,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1190,13 +1185,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337473</v>
+        <v>337535</v>
       </c>
       <c r="R6" t="n">
-        <v>6396849</v>
+        <v>6396924</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,12 +1215,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1240,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1256,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293033</v>
+        <v>122291936</v>
       </c>
       <c r="B7" t="n">
-        <v>58079</v>
+        <v>58234</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,20 +1263,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103055</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1294,9 +1289,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337554</v>
+        <v>337654</v>
       </c>
       <c r="R7" t="n">
-        <v>6396883</v>
+        <v>6396873</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293798</v>
+        <v>122293942</v>
       </c>
       <c r="B2" t="n">
-        <v>57916</v>
+        <v>56826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337473</v>
+        <v>337617</v>
       </c>
       <c r="R2" t="n">
-        <v>6396849</v>
+        <v>6396884</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293942</v>
+        <v>122291895</v>
       </c>
       <c r="B3" t="n">
-        <v>56826</v>
+        <v>56266</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337617</v>
+        <v>337542</v>
       </c>
       <c r="R3" t="n">
-        <v>6396884</v>
+        <v>6396827</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -905,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291895</v>
+        <v>122291893</v>
       </c>
       <c r="B4" t="n">
         <v>56266</v>
@@ -941,7 +937,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -950,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337542</v>
+        <v>337535</v>
       </c>
       <c r="R4" t="n">
-        <v>6396827</v>
+        <v>6396829</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1131,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291921</v>
+        <v>122291936</v>
       </c>
       <c r="B6" t="n">
-        <v>58206</v>
+        <v>58234</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1185,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337535</v>
+        <v>337654</v>
       </c>
       <c r="R6" t="n">
-        <v>6396924</v>
+        <v>6396873</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,12 +1211,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1236,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1251,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291936</v>
+        <v>122291921</v>
       </c>
       <c r="B7" t="n">
-        <v>58234</v>
+        <v>58206</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,21 +1263,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1305,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337654</v>
+        <v>337535</v>
       </c>
       <c r="R7" t="n">
-        <v>6396873</v>
+        <v>6396924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,12 +1331,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1356,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1371,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291893</v>
+        <v>122293798</v>
       </c>
       <c r="B8" t="n">
-        <v>56266</v>
+        <v>57916</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,31 +1379,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337535</v>
+        <v>337473</v>
       </c>
       <c r="R8" t="n">
-        <v>6396829</v>
+        <v>6396849</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293942</v>
+        <v>122291921</v>
       </c>
       <c r="B2" t="n">
-        <v>56826</v>
+        <v>58206</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,9 +713,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337617</v>
+        <v>337535</v>
       </c>
       <c r="R2" t="n">
-        <v>6396884</v>
+        <v>6396924</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291895</v>
+        <v>122291936</v>
       </c>
       <c r="B3" t="n">
-        <v>56266</v>
+        <v>58234</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +807,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337542</v>
+        <v>337654</v>
       </c>
       <c r="R3" t="n">
-        <v>6396827</v>
+        <v>6396873</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +879,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291893</v>
+        <v>122293798</v>
       </c>
       <c r="B4" t="n">
-        <v>56266</v>
+        <v>57916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +927,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337535</v>
+        <v>337473</v>
       </c>
       <c r="R4" t="n">
-        <v>6396829</v>
+        <v>6396849</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,12 +994,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1019,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1012,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293033</v>
+        <v>122293942</v>
       </c>
       <c r="B5" t="n">
-        <v>58079</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,25 +1042,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1061,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337554</v>
+        <v>337617</v>
       </c>
       <c r="R5" t="n">
-        <v>6396883</v>
+        <v>6396884</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1091,12 +1109,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291936</v>
+        <v>122291893</v>
       </c>
       <c r="B6" t="n">
-        <v>58234</v>
+        <v>56266</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,40 +1157,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1181,13 +1190,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337654</v>
+        <v>337535</v>
       </c>
       <c r="R6" t="n">
-        <v>6396873</v>
+        <v>6396829</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,12 +1220,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291921</v>
+        <v>122291895</v>
       </c>
       <c r="B7" t="n">
-        <v>58206</v>
+        <v>56266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,40 +1268,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208245</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337535</v>
+        <v>337542</v>
       </c>
       <c r="R7" t="n">
-        <v>6396924</v>
+        <v>6396827</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122293798</v>
+        <v>122293033</v>
       </c>
       <c r="B8" t="n">
-        <v>57916</v>
+        <v>58079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,25 +1379,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102990</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337473</v>
+        <v>337554</v>
       </c>
       <c r="R8" t="n">
-        <v>6396849</v>
+        <v>6396883</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291921</v>
+        <v>122293033</v>
       </c>
       <c r="B2" t="n">
-        <v>58206</v>
+        <v>58084</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>103055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,14 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337535</v>
+        <v>337554</v>
       </c>
       <c r="R2" t="n">
-        <v>6396924</v>
+        <v>6396883</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291936</v>
+        <v>122293798</v>
       </c>
       <c r="B3" t="n">
-        <v>58234</v>
+        <v>57921</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,14 +828,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337654</v>
+        <v>337473</v>
       </c>
       <c r="R3" t="n">
-        <v>6396873</v>
+        <v>6396849</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +894,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -915,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293798</v>
+        <v>122291921</v>
       </c>
       <c r="B4" t="n">
-        <v>57916</v>
+        <v>58211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +921,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -953,9 +943,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337473</v>
+        <v>337535</v>
       </c>
       <c r="R4" t="n">
-        <v>6396849</v>
+        <v>6396924</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,12 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1030,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293942</v>
+        <v>122291936</v>
       </c>
       <c r="B5" t="n">
-        <v>56826</v>
+        <v>58239</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1068,9 +1063,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337617</v>
+        <v>337654</v>
       </c>
       <c r="R5" t="n">
-        <v>6396884</v>
+        <v>6396873</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291893</v>
+        <v>122291895</v>
       </c>
       <c r="B6" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337535</v>
+        <v>337542</v>
       </c>
       <c r="R6" t="n">
-        <v>6396829</v>
+        <v>6396827</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291895</v>
+        <v>122293942</v>
       </c>
       <c r="B7" t="n">
-        <v>56266</v>
+        <v>56831</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,31 +1268,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>102954</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1301,13 +1305,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337542</v>
+        <v>337617</v>
       </c>
       <c r="R7" t="n">
-        <v>6396827</v>
+        <v>6396884</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,12 +1335,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,7 +1360,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1367,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122293033</v>
+        <v>122291893</v>
       </c>
       <c r="B8" t="n">
-        <v>58079</v>
+        <v>56271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,31 +1387,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337554</v>
+        <v>337535</v>
       </c>
       <c r="R8" t="n">
-        <v>6396883</v>
+        <v>6396829</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293033</v>
+        <v>122293942</v>
       </c>
       <c r="B2" t="n">
-        <v>58084</v>
+        <v>56831</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337554</v>
+        <v>337617</v>
       </c>
       <c r="R2" t="n">
-        <v>6396883</v>
+        <v>6396884</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293798</v>
+        <v>122291893</v>
       </c>
       <c r="B3" t="n">
-        <v>57921</v>
+        <v>56271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337473</v>
+        <v>337535</v>
       </c>
       <c r="R3" t="n">
-        <v>6396849</v>
+        <v>6396829</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1256,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293942</v>
+        <v>122293798</v>
       </c>
       <c r="B7" t="n">
-        <v>56831</v>
+        <v>57921</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,16 +1268,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1305,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337617</v>
+        <v>337473</v>
       </c>
       <c r="R7" t="n">
-        <v>6396884</v>
+        <v>6396849</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1335,12 +1331,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291893</v>
+        <v>122293033</v>
       </c>
       <c r="B8" t="n">
-        <v>56271</v>
+        <v>58084</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,27 +1383,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337535</v>
+        <v>337554</v>
       </c>
       <c r="R8" t="n">
-        <v>6396829</v>
+        <v>6396883</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293942</v>
+        <v>122291893</v>
       </c>
       <c r="B2" t="n">
-        <v>56831</v>
+        <v>56271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337617</v>
+        <v>337535</v>
       </c>
       <c r="R2" t="n">
-        <v>6396884</v>
+        <v>6396829</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291893</v>
+        <v>122293942</v>
       </c>
       <c r="B3" t="n">
-        <v>56271</v>
+        <v>56831</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337535</v>
+        <v>337617</v>
       </c>
       <c r="R3" t="n">
-        <v>6396829</v>
+        <v>6396884</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291893</v>
+        <v>122293798</v>
       </c>
       <c r="B2" t="n">
-        <v>56271</v>
+        <v>57921</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>102990</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337535</v>
+        <v>337473</v>
       </c>
       <c r="R2" t="n">
-        <v>6396829</v>
+        <v>6396849</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293942</v>
+        <v>122291893</v>
       </c>
       <c r="B3" t="n">
-        <v>56831</v>
+        <v>56271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +797,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Enkelbeckasin</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337617</v>
+        <v>337535</v>
       </c>
       <c r="R3" t="n">
-        <v>6396884</v>
+        <v>6396829</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291921</v>
+        <v>122291936</v>
       </c>
       <c r="B4" t="n">
-        <v>58211</v>
+        <v>58239</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +907,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vanlig padda</t>
-        </is>
+        <v>208249</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -955,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337535</v>
+        <v>337654</v>
       </c>
       <c r="R4" t="n">
-        <v>6396924</v>
+        <v>6396873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,12 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +995,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1021,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291936</v>
+        <v>122293033</v>
       </c>
       <c r="B5" t="n">
-        <v>58239</v>
+        <v>58084</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,20 +1018,15 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vanlig groda</t>
-        </is>
+        <v>103055</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,14 +1039,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1075,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337654</v>
+        <v>337554</v>
       </c>
       <c r="R5" t="n">
-        <v>6396873</v>
+        <v>6396883</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,12 +1080,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,7 +1105,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1159,11 +1134,6 @@
       <c r="E6" t="n">
         <v>205998</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -1252,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293798</v>
+        <v>122293942</v>
       </c>
       <c r="B7" t="n">
-        <v>57921</v>
+        <v>56831</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,16 +1238,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Järnsparv</t>
-        </is>
+        <v>102954</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1301,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337473</v>
+        <v>337617</v>
       </c>
       <c r="R7" t="n">
-        <v>6396849</v>
+        <v>6396884</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1331,12 +1296,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122293033</v>
+        <v>122291921</v>
       </c>
       <c r="B8" t="n">
-        <v>58084</v>
+        <v>58211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,25 +1344,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Gulsparv</t>
-        </is>
+        <v>208245</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,9 +1365,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1381,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337554</v>
+        <v>337535</v>
       </c>
       <c r="R8" t="n">
-        <v>6396883</v>
+        <v>6396924</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1411,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1436,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293798</v>
+        <v>122293033</v>
       </c>
       <c r="B2" t="n">
-        <v>57921</v>
+        <v>58088</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103055</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337473</v>
+        <v>337554</v>
       </c>
       <c r="R2" t="n">
-        <v>6396849</v>
+        <v>6396883</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -749,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291893</v>
+        <v>122291936</v>
       </c>
       <c r="B3" t="n">
-        <v>56271</v>
+        <v>58243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +802,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>208249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337535</v>
+        <v>337654</v>
       </c>
       <c r="R3" t="n">
-        <v>6396829</v>
+        <v>6396873</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,12 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291936</v>
+        <v>122293798</v>
       </c>
       <c r="B4" t="n">
-        <v>58239</v>
+        <v>57925</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,16 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>102990</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -924,14 +948,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -940,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337654</v>
+        <v>337473</v>
       </c>
       <c r="R4" t="n">
-        <v>6396873</v>
+        <v>6396849</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,12 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1006,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293033</v>
+        <v>122293942</v>
       </c>
       <c r="B5" t="n">
-        <v>58084</v>
+        <v>56835</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,20 +1037,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>102954</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1050,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337554</v>
+        <v>337617</v>
       </c>
       <c r="R5" t="n">
-        <v>6396883</v>
+        <v>6396884</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1080,12 +1104,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291895</v>
+        <v>122291893</v>
       </c>
       <c r="B6" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,6 +1158,11 @@
       <c r="E6" t="n">
         <v>205998</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -1147,7 +1176,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1156,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337542</v>
+        <v>337535</v>
       </c>
       <c r="R6" t="n">
-        <v>6396827</v>
+        <v>6396829</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1222,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293942</v>
+        <v>122291895</v>
       </c>
       <c r="B7" t="n">
-        <v>56831</v>
+        <v>56275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,30 +1263,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102954</v>
+        <v>205998</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1266,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337617</v>
+        <v>337542</v>
       </c>
       <c r="R7" t="n">
-        <v>6396884</v>
+        <v>6396827</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,12 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,7 +1351,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1335,7 +1365,7 @@
         <v>122291921</v>
       </c>
       <c r="B8" t="n">
-        <v>58211</v>
+        <v>58215</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,6 +1379,11 @@
       </c>
       <c r="E8" t="n">
         <v>208245</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293033</v>
+        <v>122291893</v>
       </c>
       <c r="B2" t="n">
-        <v>58088</v>
+        <v>56275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337554</v>
+        <v>337535</v>
       </c>
       <c r="R2" t="n">
-        <v>6396883</v>
+        <v>6396829</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291936</v>
+        <v>122293942</v>
       </c>
       <c r="B3" t="n">
-        <v>58243</v>
+        <v>56835</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,14 +824,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337654</v>
+        <v>337617</v>
       </c>
       <c r="R3" t="n">
-        <v>6396873</v>
+        <v>6396884</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -910,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293798</v>
+        <v>122291921</v>
       </c>
       <c r="B4" t="n">
-        <v>57925</v>
+        <v>58215</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,16 +917,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -948,9 +939,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337473</v>
+        <v>337535</v>
       </c>
       <c r="R4" t="n">
-        <v>6396849</v>
+        <v>6396924</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1010,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293942</v>
+        <v>122293798</v>
       </c>
       <c r="B5" t="n">
-        <v>56835</v>
+        <v>57925</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,16 +1037,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1074,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337617</v>
+        <v>337473</v>
       </c>
       <c r="R5" t="n">
-        <v>6396884</v>
+        <v>6396849</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1104,12 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291893</v>
+        <v>122291895</v>
       </c>
       <c r="B6" t="n">
         <v>56275</v>
@@ -1176,7 +1172,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1185,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337535</v>
+        <v>337542</v>
       </c>
       <c r="R6" t="n">
-        <v>6396829</v>
+        <v>6396827</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1251,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291895</v>
+        <v>122291936</v>
       </c>
       <c r="B7" t="n">
-        <v>56275</v>
+        <v>58243</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,31 +1259,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1296,13 +1301,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337542</v>
+        <v>337654</v>
       </c>
       <c r="R7" t="n">
-        <v>6396827</v>
+        <v>6396873</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,12 +1331,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291921</v>
+        <v>122293033</v>
       </c>
       <c r="B8" t="n">
-        <v>58215</v>
+        <v>58088</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1379,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1400,14 +1405,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337535</v>
+        <v>337554</v>
       </c>
       <c r="R8" t="n">
-        <v>6396924</v>
+        <v>6396883</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291893</v>
+        <v>122293942</v>
       </c>
       <c r="B2" t="n">
-        <v>56275</v>
+        <v>56835</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337535</v>
+        <v>337617</v>
       </c>
       <c r="R2" t="n">
-        <v>6396829</v>
+        <v>6396884</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293942</v>
+        <v>122291893</v>
       </c>
       <c r="B3" t="n">
-        <v>56835</v>
+        <v>56275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337617</v>
+        <v>337535</v>
       </c>
       <c r="R3" t="n">
-        <v>6396884</v>
+        <v>6396829</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291921</v>
+        <v>122293033</v>
       </c>
       <c r="B4" t="n">
-        <v>58215</v>
+        <v>58088</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,25 +913,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,14 +939,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -955,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337535</v>
+        <v>337554</v>
       </c>
       <c r="R4" t="n">
-        <v>6396924</v>
+        <v>6396883</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1005,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293798</v>
+        <v>122291921</v>
       </c>
       <c r="B5" t="n">
-        <v>57925</v>
+        <v>58215</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,9 +1054,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337473</v>
+        <v>337535</v>
       </c>
       <c r="R5" t="n">
-        <v>6396849</v>
+        <v>6396924</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291895</v>
+        <v>122291936</v>
       </c>
       <c r="B6" t="n">
-        <v>56275</v>
+        <v>58243</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,31 +1148,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1181,13 +1190,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337542</v>
+        <v>337654</v>
       </c>
       <c r="R6" t="n">
-        <v>6396827</v>
+        <v>6396873</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,12 +1220,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291936</v>
+        <v>122293798</v>
       </c>
       <c r="B7" t="n">
-        <v>58243</v>
+        <v>57925</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,21 +1272,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1285,14 +1294,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1301,13 +1305,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337654</v>
+        <v>337473</v>
       </c>
       <c r="R7" t="n">
-        <v>6396873</v>
+        <v>6396849</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,12 +1335,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,7 +1360,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1367,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122293033</v>
+        <v>122291895</v>
       </c>
       <c r="B8" t="n">
-        <v>58088</v>
+        <v>56275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,31 +1387,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337554</v>
+        <v>337542</v>
       </c>
       <c r="R8" t="n">
-        <v>6396883</v>
+        <v>6396827</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293942</v>
+        <v>122293798</v>
       </c>
       <c r="B2" t="n">
-        <v>56835</v>
+        <v>57925</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337617</v>
+        <v>337473</v>
       </c>
       <c r="R2" t="n">
-        <v>6396884</v>
+        <v>6396849</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291893</v>
+        <v>122291895</v>
       </c>
       <c r="B3" t="n">
         <v>56275</v>
@@ -826,7 +826,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337535</v>
+        <v>337542</v>
       </c>
       <c r="R3" t="n">
-        <v>6396829</v>
+        <v>6396827</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293033</v>
+        <v>122291936</v>
       </c>
       <c r="B4" t="n">
-        <v>58088</v>
+        <v>58243</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,20 +913,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,9 +939,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -950,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337554</v>
+        <v>337654</v>
       </c>
       <c r="R4" t="n">
-        <v>6396883</v>
+        <v>6396873</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,7 +1010,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291921</v>
+        <v>122293942</v>
       </c>
       <c r="B5" t="n">
-        <v>58215</v>
+        <v>56835</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1037,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,14 +1059,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337535</v>
+        <v>337617</v>
       </c>
       <c r="R5" t="n">
-        <v>6396924</v>
+        <v>6396884</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291936</v>
+        <v>122291921</v>
       </c>
       <c r="B6" t="n">
-        <v>58243</v>
+        <v>58215</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,21 +1152,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337654</v>
+        <v>337535</v>
       </c>
       <c r="R6" t="n">
-        <v>6396873</v>
+        <v>6396924</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1256,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122293798</v>
+        <v>122291893</v>
       </c>
       <c r="B7" t="n">
-        <v>57925</v>
+        <v>56275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,35 +1268,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337473</v>
+        <v>337535</v>
       </c>
       <c r="R7" t="n">
-        <v>6396849</v>
+        <v>6396829</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,12 +1331,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1356,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1371,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291895</v>
+        <v>122293033</v>
       </c>
       <c r="B8" t="n">
-        <v>56275</v>
+        <v>58088</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,27 +1383,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337542</v>
+        <v>337554</v>
       </c>
       <c r="R8" t="n">
-        <v>6396827</v>
+        <v>6396883</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293798</v>
+        <v>122291893</v>
       </c>
       <c r="B2" t="n">
-        <v>57925</v>
+        <v>56275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337473</v>
+        <v>337535</v>
       </c>
       <c r="R2" t="n">
-        <v>6396849</v>
+        <v>6396829</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291895</v>
+        <v>122293033</v>
       </c>
       <c r="B3" t="n">
-        <v>56275</v>
+        <v>58088</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,27 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337542</v>
+        <v>337554</v>
       </c>
       <c r="R3" t="n">
-        <v>6396827</v>
+        <v>6396883</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291936</v>
+        <v>122291921</v>
       </c>
       <c r="B4" t="n">
-        <v>58243</v>
+        <v>58215</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337654</v>
+        <v>337535</v>
       </c>
       <c r="R4" t="n">
-        <v>6396873</v>
+        <v>6396924</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291921</v>
+        <v>122293798</v>
       </c>
       <c r="B6" t="n">
-        <v>58215</v>
+        <v>57925</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208245</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1174,14 +1174,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1190,13 +1185,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337535</v>
+        <v>337473</v>
       </c>
       <c r="R6" t="n">
-        <v>6396924</v>
+        <v>6396849</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,12 +1215,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1240,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1256,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291893</v>
+        <v>122291936</v>
       </c>
       <c r="B7" t="n">
-        <v>56275</v>
+        <v>58243</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,31 +1263,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1301,13 +1305,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337535</v>
+        <v>337654</v>
       </c>
       <c r="R7" t="n">
-        <v>6396829</v>
+        <v>6396873</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,12 +1335,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122293033</v>
+        <v>122291895</v>
       </c>
       <c r="B8" t="n">
-        <v>58088</v>
+        <v>56275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,31 +1387,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337554</v>
+        <v>337542</v>
       </c>
       <c r="R8" t="n">
-        <v>6396883</v>
+        <v>6396827</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291893</v>
+        <v>122293798</v>
       </c>
       <c r="B2" t="n">
-        <v>56275</v>
+        <v>57926</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337535</v>
+        <v>337473</v>
       </c>
       <c r="R2" t="n">
-        <v>6396829</v>
+        <v>6396849</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293033</v>
+        <v>122291893</v>
       </c>
       <c r="B3" t="n">
-        <v>58088</v>
+        <v>56276</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +806,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337554</v>
+        <v>337535</v>
       </c>
       <c r="R3" t="n">
-        <v>6396883</v>
+        <v>6396829</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291921</v>
+        <v>122293033</v>
       </c>
       <c r="B4" t="n">
-        <v>58215</v>
+        <v>58089</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,25 +913,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,14 +939,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -955,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337535</v>
+        <v>337554</v>
       </c>
       <c r="R4" t="n">
-        <v>6396924</v>
+        <v>6396883</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1005,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293942</v>
+        <v>122291921</v>
       </c>
       <c r="B5" t="n">
-        <v>56835</v>
+        <v>58216</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,9 +1054,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337617</v>
+        <v>337535</v>
       </c>
       <c r="R5" t="n">
-        <v>6396884</v>
+        <v>6396924</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293798</v>
+        <v>122293942</v>
       </c>
       <c r="B6" t="n">
-        <v>57925</v>
+        <v>56836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337473</v>
+        <v>337617</v>
       </c>
       <c r="R6" t="n">
-        <v>6396849</v>
+        <v>6396884</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291936</v>
+        <v>122291895</v>
       </c>
       <c r="B7" t="n">
-        <v>58243</v>
+        <v>56276</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,40 +1263,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337654</v>
+        <v>337542</v>
       </c>
       <c r="R7" t="n">
-        <v>6396873</v>
+        <v>6396827</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,12 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291895</v>
+        <v>122291936</v>
       </c>
       <c r="B8" t="n">
-        <v>56275</v>
+        <v>58244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,31 +1374,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337542</v>
+        <v>337654</v>
       </c>
       <c r="R8" t="n">
-        <v>6396827</v>
+        <v>6396873</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291921</v>
+        <v>122293942</v>
       </c>
       <c r="B5" t="n">
-        <v>58216</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,14 +1054,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337535</v>
+        <v>337617</v>
       </c>
       <c r="R5" t="n">
-        <v>6396924</v>
+        <v>6396884</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,12 +1095,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1136,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122293942</v>
+        <v>122291921</v>
       </c>
       <c r="B6" t="n">
-        <v>56836</v>
+        <v>58216</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,16 +1147,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102954</v>
+        <v>208245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1174,9 +1169,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337617</v>
+        <v>337535</v>
       </c>
       <c r="R6" t="n">
-        <v>6396884</v>
+        <v>6396924</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122293798</v>
+        <v>122291893</v>
       </c>
       <c r="B2" t="n">
-        <v>57926</v>
+        <v>56276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337473</v>
+        <v>337535</v>
       </c>
       <c r="R2" t="n">
-        <v>6396849</v>
+        <v>6396829</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291893</v>
+        <v>122293798</v>
       </c>
       <c r="B3" t="n">
-        <v>56276</v>
+        <v>57926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337535</v>
+        <v>337473</v>
       </c>
       <c r="R3" t="n">
-        <v>6396829</v>
+        <v>6396849</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291895</v>
+        <v>122291936</v>
       </c>
       <c r="B7" t="n">
-        <v>56276</v>
+        <v>58244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,31 +1263,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1296,13 +1305,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337542</v>
+        <v>337654</v>
       </c>
       <c r="R7" t="n">
-        <v>6396827</v>
+        <v>6396873</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,12 +1335,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291936</v>
+        <v>122291895</v>
       </c>
       <c r="B8" t="n">
-        <v>58244</v>
+        <v>56276</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,40 +1383,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337654</v>
+        <v>337542</v>
       </c>
       <c r="R8" t="n">
-        <v>6396873</v>
+        <v>6396827</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 3648-2021 artfynd.xlsx
+++ b/artfynd/A 3648-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291893</v>
+        <v>122291921</v>
       </c>
       <c r="B2" t="n">
-        <v>56276</v>
+        <v>58216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -723,10 +732,10 @@
         <v>337535</v>
       </c>
       <c r="R2" t="n">
-        <v>6396829</v>
+        <v>6396924</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,12 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122293798</v>
+        <v>122291893</v>
       </c>
       <c r="B3" t="n">
-        <v>57926</v>
+        <v>56276</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +807,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337473</v>
+        <v>337535</v>
       </c>
       <c r="R3" t="n">
-        <v>6396849</v>
+        <v>6396829</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122293033</v>
+        <v>122293942</v>
       </c>
       <c r="B4" t="n">
-        <v>58089</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,25 +918,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -950,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337554</v>
+        <v>337617</v>
       </c>
       <c r="R4" t="n">
-        <v>6396883</v>
+        <v>6396884</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -980,12 +985,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122293942</v>
+        <v>122291936</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
+        <v>58244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,9 +1059,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337617</v>
+        <v>337654</v>
       </c>
       <c r="R5" t="n">
-        <v>6396884</v>
+        <v>6396873</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,12 +1105,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1130,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1131,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291921</v>
+        <v>122293033</v>
       </c>
       <c r="B6" t="n">
-        <v>58216</v>
+        <v>58089</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1153,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208245</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1169,14 +1179,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1185,13 +1190,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337535</v>
+        <v>337554</v>
       </c>
       <c r="R6" t="n">
-        <v>6396924</v>
+        <v>6396883</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,12 +1220,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1245,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1251,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291936</v>
+        <v>122291895</v>
       </c>
       <c r="B7" t="n">
-        <v>58244</v>
+        <v>56276</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,40 +1268,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>337654</v>
+        <v>337542</v>
       </c>
       <c r="R7" t="n">
-        <v>6396873</v>
+        <v>6396827</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,12 +1331,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291895</v>
+        <v>122293798</v>
       </c>
       <c r="B8" t="n">
-        <v>56276</v>
+        <v>57926</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,31 +1379,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>102990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>aktiv</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>337542</v>
+        <v>337473</v>
       </c>
       <c r="R8" t="n">
-        <v>6396827</v>
+        <v>6396849</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
